--- a/conformance/fixtures/054-empty-list-membership/template.xlsx
+++ b/conformance/fixtures/054-empty-list-membership/template.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
-    <sheet sheetId="2" name="_Allowed" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
+    <sheet sheetId="2" name="__lists__" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Report" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>name</t>
   </si>
@@ -39,6 +39,9 @@
     <t>output.xlsx</t>
   </si>
   <si>
+    <t>Allowed</t>
+  </si>
+  <si>
     <t>Acme</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>{{ @filter [Customer] in _Allowed }}</t>
+    <t>{{ @filter [Customer] in __lists__[Allowed] }}</t>
   </si>
   <si>
     <t>{{ [Customer] }}</t>
@@ -483,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -504,6 +507,11 @@
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -519,23 +527,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
